--- a/data/submission/FILLIT_CAFU_Affected_Accounts.xlsx
+++ b/data/submission/FILLIT_CAFU_Affected_Accounts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAFU mentions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CAFU mentions'!$A$1:$X$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CAFU mentions'!$A$1:$W$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -494,19 +494,18 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="60" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="60" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -567,65 +566,60 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Direct no.</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Current supplier</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Current supplier</t>
+          <t>Consumption (as recorded)</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Consumption (as recorded)</t>
+          <t>Est. litres / month</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Est. litres / month</t>
+          <t>Fleet / equipment</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Fleet / equipment</t>
+          <t>Pain points</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Pain points</t>
+          <t>Latest comments</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Latest comments</t>
+          <t>First visit</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>First visit</t>
+          <t>Last visit</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Last visit</t>
+          <t>Visits</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Visits</t>
+          <t>Lead source</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Lead source</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Mentions CAFU</t>
         </is>
@@ -684,59 +678,54 @@
           <t>+971 55 902 0311/+971 52 252 1047</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>522478874</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Third party</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Third party</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
           <t>2000G/Week</t>
         </is>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="O2" s="2" t="n">
         <v>32778</v>
       </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>18 Forklifts, 3 Passenger vans, 4 Trailers, 2 Burners</t>
+        </is>
+      </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>18 Forklifts, 3 Passenger vans, 4 Trailers, 2 Burners</t>
+          <t>ENOC and ADNOC Price is high</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>ENOC and ADNOC Price is high</t>
+          <t>ADNOC is hard to get contract, enquired about freezone delivery - Hamriya, faced problems with CAFU, Asked for delivery charges, Looking for bulk rate and better than ADNOC price, Due to war consumption has reduced to half</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>ADNOC is hard to get contract, enquired about freezone delivery - Hamriya, faced problems with CAFU, Asked for delivery charges, Looking for bulk rate and better than ADNOC price, Due to war consumption has reduced to half</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="U2" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -794,38 +783,38 @@
           <t>971 6 542 0662</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>528312108</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Al Nasr diesel</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Al Nasr diesel</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
           <t>2500L/month</t>
         </is>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="O3" s="2" t="n">
         <v>2500</v>
       </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>1trailer, 2 bulker, 4 forklifts</t>
+        </is>
+      </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>1trailer, 2 bulker, 4 forklifts</t>
+          <t>Vehicle go to fuel stations to fill</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>Vehicle go to fuel stations to fill</t>
+          <t>They used to take from Cafu,but cafu stopped delivering</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>They used to take from Cafu,but cafu stopped delivering</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
@@ -833,20 +822,15 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="n">
+      <c r="U3" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -908,40 +892,40 @@
           <t>971 4 399 9211</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>503612096</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Procured from CAFU earlier. Currently procuring from other 3rd party</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Procured from CAFU earlier. Currently procuring from other 3rd party</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
           <t>10000AED+ per month</t>
         </is>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="O4" s="2" t="n">
         <v>2500</v>
       </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5+ (1 bus, 1 forklift, 1 3ton truck, 1 6ton truck, 1 500L drum)</t>
+        </is>
+      </c>
       <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>5+ (1 bus, 1 forklift, 1 3ton truck, 1 6ton truck, 1 500L drum)</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>CAFU not coming to site.
 - 3rd suppliers have bad quality.
 - Extra charges</t>
         </is>
       </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Very intrested so gave Sharukh sir's number</t>
+        </is>
+      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>Very intrested so gave Sharukh sir's number</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -949,20 +933,15 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="n">
+      <c r="U4" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1021,33 +1000,37 @@
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>ENOC, CAFU, other 3rd parties</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>ENOC, CAFU, other 3rd parties</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
           <t>1500L based on requirement</t>
         </is>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="O5" s="2" t="n">
         <v>1500</v>
       </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>20(12 forklifts, 3 trucks, 1 crane, 4-5 other vehicles)</t>
+        </is>
+      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>20(12 forklifts, 3 trucks, 1 crane, 4-5 other vehicles)</t>
+          <t>CAFU application is not working most of the times. Bad quality diesel from other 3rd parties. ADNOC not delivering small quantities.</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>CAFU application is not working most of the times. Bad quality diesel from other 3rd parties. ADNOC not delivering small quantities.</t>
+          <t>Very intrested</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>Very intrested</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1055,20 +1038,15 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="n">
+      <c r="U5" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1122,38 +1100,42 @@
           <t>: 04 370 6944</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Golden Power - ENOC</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Golden Power - ENOC</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
           <t>5000 AED for each vechile not for heavy vechiles, They have Generators which cost 15000 AED in a month</t>
         </is>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="O6" s="2" t="n">
         <v>1250</v>
       </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>15 Vehichles and Few Generators</t>
+        </is>
+      </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>15 Vehichles and Few Generators</t>
+          <t>Low quality fuel is reducing their vehicle's efficiency</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>Low quality fuel is reducing their vehicle's efficiency</t>
+          <t>They are buying from the third party and CAFU. they are buying petrol from CAFU and they are cost focused and enquired about extra charge and discounts</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>They are buying from the third party and CAFU. they are buying petrol from CAFU and they are cost focused and enquired about extra charge and discounts</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1161,20 +1143,15 @@
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="n">
+      <c r="U6" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1232,59 +1209,54 @@
           <t>+971-6-5350852</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>555636014</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Nearest fuel station</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Nearest fuel station</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
           <t>2500AED/month+</t>
         </is>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="O7" s="2" t="n">
         <v>625</v>
       </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3 heavy pickups</t>
+        </is>
+      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>3 heavy pickups</t>
+          <t>CAFU has high charger</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>CAFU has high charger</t>
+          <t>Tried CAFU but left beacuse of charges</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>Tried CAFU but left beacuse of charges</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="V7" s="2" t="n">
+      <c r="U7" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1338,56 +1310,51 @@
           <t>04 347 3400</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>522434524</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Fuel station and 3rd party</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Fuel station and 3rd party</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
           <t>10000 Gallons / month</t>
         </is>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="O8" s="2" t="n">
         <v>37850</v>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>40+(12 forklifts, 30+ trucks)</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>Asked to share more details (price, credits etc. through whatsapp)
 -CAFU is not delivering to them</t>
         </is>
       </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="n">
+      <c r="U8" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1447,40 +1414,40 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>552573364</t>
+          <t>aimee.m@dayalmc.com / dheepa@dayalmc.com /sales@dayalmc.com</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>aimee.m@dayalmc.com / dheepa@dayalmc.com /sales@dayalmc.com</t>
+          <t>ADNOC (chip)</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>ADNOC (chip)</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
           <t>30000L/month+</t>
         </is>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>30000</v>
       </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>7 forklift, 10 pickups, 1 trailer</t>
+        </is>
+      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>7 forklift, 10 pickups, 1 trailer</t>
+          <t>CAFU is not filling on site</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>CAFU is not filling on site</t>
+          <t>CAFU not delivering</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>CAFU not delivering</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
@@ -1488,20 +1455,15 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="n">
+      <c r="U9" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1559,38 +1521,38 @@
           <t>971 6 554 9593</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>561183329</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>ADNOC (prepaid card)</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>ADNOC (prepaid card)</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
           <t>20000L/month (both diesel &amp; petrol)</t>
         </is>
       </c>
-      <c r="P10" s="2" t="n">
+      <c r="O10" s="2" t="n">
         <v>20000</v>
       </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>12 vehicles</t>
+        </is>
+      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>12 vehicles</t>
+          <t>Trust issue with CAFU (took credits)</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>Trust issue with CAFU (took credits)</t>
+          <t>Contract with CAFU in 2025 but they stole their credit</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>Contract with CAFU in 2025 but they stole their credit</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1598,20 +1560,15 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="n">
+      <c r="U10" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1665,39 +1622,43 @@
           <t>44178642</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>mail@dar-al-rokham.com</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>mail@dar-al-rokham.com</t>
+          <t>ADNOC / ENOC</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>ADNOC / ENOC</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
           <t>50000 AED+ ( 9000AED+ for forklifts at site, rest for other vehicles)</t>
         </is>
       </c>
-      <c r="P11" s="2" t="n">
+      <c r="O11" s="2" t="n">
         <v>12500</v>
       </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>13+ (3 forklifts, 1 generation, 4 3-ton trucks, 4 6-ton trucks, 1 crane and others)</t>
+        </is>
+      </c>
       <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>13+ (3 forklifts, 1 generation, 4 3-ton trucks, 4 6-ton trucks, 1 crane and others)</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>Diesel quality of 3rd party suppliers is not good
 - CAFU not supplying</t>
         </is>
       </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>Multiple offices</t>
+        </is>
+      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>Multiple offices</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1705,20 +1666,15 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="n">
+      <c r="U11" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
       <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>Self-generated</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1777,39 +1733,38 @@
           <t>971 4 221 1782</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>Shafil - 0503283454
-Shakil - 0501604847</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>ADNOC (fuel station)</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>ADNOC (fuel station)</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
           <t>10000L/month</t>
         </is>
       </c>
-      <c r="P12" s="2" t="n">
+      <c r="O12" s="2" t="n">
         <v>10000</v>
       </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>12 trucks</t>
+        </is>
+      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>12 trucks</t>
+          <t>CAFU stopped delivering</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>CAFU stopped delivering</t>
+          <t>Used to get from CAFU, but CAFU stopped operations</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>Used to get from CAFU, but CAFU stopped operations</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -1817,20 +1772,15 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="n">
+      <c r="U12" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X12" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1884,61 +1834,56 @@
           <t>971-4-4326581</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>554997262</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>ENOC (chip)</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>ENOC (chip)</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>8500 l/month+ (for months)
 1850 l/month+ (for forklifts)</t>
         </is>
       </c>
-      <c r="P13" s="2" t="n">
+      <c r="O13" s="2" t="n">
         <v>8500</v>
       </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>6 trucks, 3 forklifts</t>
+        </is>
+      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>6 trucks, 3 forklifts</t>
+          <t>Looking for some USP</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>Looking for some USP</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>Operating in multiple countries
 - Currently using go fuel ( CAFU stopped delivering)</t>
         </is>
       </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="n">
+      <c r="U13" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
       <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>Self-generated</t>
-        </is>
-      </c>
-      <c r="X13" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1996,60 +1941,55 @@
           <t>+971 4 885 6340</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>585585663</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Aquiring from FuelBuddy and ADNOC currently. Earlier acquired from CAFU</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Aquiring from FuelBuddy and ADNOC currently. Earlier acquired from CAFU</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
           <t>4000-5000L/month(boiler) . Unknown for forklifts &amp; trucks</t>
         </is>
       </c>
-      <c r="P14" s="2" t="n">
+      <c r="O14" s="2" t="n">
         <v>4500</v>
       </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>12+(7-8 forklifts, 5+trucks)</t>
+        </is>
+      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>12+(7-8 forklifts, 5+trucks)</t>
+          <t>CAFU stopped delivering</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>CAFU stopped delivering</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>Asked for sample and price.
 - They have a transport company as well(space lead transportation)</t>
         </is>
       </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="n">
+      <c r="U14" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2099,34 +2039,34 @@
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>581032667</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Third party (bedford fuel trading)</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Third party (bedford fuel trading)</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
           <t>2000L/month</t>
         </is>
       </c>
-      <c r="P15" s="2" t="n">
+      <c r="O15" s="2" t="n">
         <v>2000</v>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>1 bus, 2 forklifts</t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>Tried CAFU for petrol</t>
+        </is>
+      </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>Tried CAFU for petrol</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
@@ -2134,20 +2074,15 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="n">
+      <c r="U15" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
       <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>Self-generated</t>
-        </is>
-      </c>
-      <c r="X15" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2205,34 +2140,34 @@
           <t>557622755</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>557622755</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>CAFU</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>CAFU</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
           <t>5000 AED/month+</t>
         </is>
       </c>
-      <c r="P16" s="2" t="n">
+      <c r="O16" s="2" t="n">
         <v>1250</v>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Delivery fee</t>
+        </is>
+      </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>Delivery fee</t>
+          <t>Getting from CAFU with extra delivery fee</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>Getting from CAFU with extra delivery fee</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2240,20 +2175,15 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="n">
+      <c r="U16" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
       <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>Self-generated</t>
-        </is>
-      </c>
-      <c r="X16" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2300,27 +2230,31 @@
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>Multiple vedors(cafu, enoc)</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="n"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>50+ Vechiles</t>
+        </is>
+      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>50+ Vechiles</t>
+          <t>Don't trust vendors because of price.</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>Don't trust vendors because of price.</t>
+          <t>No monthly contracts due to price fluctuation. Got business card(Rahul) - very knowledgeble. Knows diesel quality and test it. Pain point - Don't trust vendors because of price. Very intrested in companies who provide credit.</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>No monthly contracts due to price fluctuation. Got business card(Rahul) - very knowledgeble. Knows diesel quality and test it. Pain point - Don't trust vendors because of price. Very intrested in companies who provide credit.</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2328,20 +2262,15 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="n">
+      <c r="U17" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X17" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2399,33 +2328,33 @@
           <t>971 6 533 8751</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>544591752</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>Emarat (pump)</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="n"/>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>3 trailers(10t, 4t, 3t), 4 forklifts(10t, 5t, 4t, 3t)
  t = Tons</t>
         </is>
       </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>CAFU not filling forklifts</t>
+        </is>
+      </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>CAFU not filling forklifts</t>
+          <t>Asked for diesel sample for quality check</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>Asked for diesel sample for quality check</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -2433,20 +2362,15 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="n">
+      <c r="U18" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X18" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2501,33 +2425,37 @@
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Fuel pumps</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>Fuel pumps</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Less consumption in dubai(1 truck).
 - Unknown consumption in UAQ</t>
         </is>
       </c>
-      <c r="P19" s="2" t="n"/>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="n"/>
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>1 in Dubai.
 - Unknown inUAQ</t>
         </is>
       </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Earlier used to procure from CAFU. Stopped due to bad service</t>
+        </is>
+      </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>Earlier used to procure from CAFU. Stopped due to bad service</t>
+          <t>Also operating in Um Al Quwain</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>Also operating in Um Al Quwain</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -2535,20 +2463,15 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="n">
+      <c r="U19" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X19" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2602,50 +2525,45 @@
           <t>04 330 0071</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>565332951</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>ENOC</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="n"/>
-      <c r="Q20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>13 vehicles (3+buses, 4+pickups, 1 tipper, 2 forklifts)</t>
         </is>
       </c>
-      <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>Fuel required at sites
 - Tried CAFU earlier</t>
         </is>
       </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="n">
+      <c r="U20" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Planned list</t>
+        </is>
+      </c>
       <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>Planned list</t>
-        </is>
-      </c>
-      <c r="X20" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2700,29 +2618,33 @@
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>ENOC (prepaid chip)</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>ENOC (prepaid chip)</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
           <t>2000 aed/month</t>
         </is>
       </c>
-      <c r="P21" s="2" t="n">
+      <c r="O21" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>1 pickup, 2 vans</t>
         </is>
       </c>
-      <c r="R21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Fased timing issue with CAFU</t>
+        </is>
+      </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>Fased timing issue with CAFU</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
@@ -2730,27 +2652,22 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="n">
+      <c r="U21" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Self-generated</t>
+        </is>
+      </c>
       <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>Self-generated</t>
-        </is>
-      </c>
-      <c r="X21" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X21"/>
+  <autoFilter ref="A1:W21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>